--- a/artfynd/A 22842-2022 artfynd.xlsx
+++ b/artfynd/A 22842-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22842-2022 artfynd.xlsx
+++ b/artfynd/A 22842-2022 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>103812205</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380900.147975298</v>
+        <v>380900</v>
       </c>
       <c r="R2" t="n">
-        <v>6292619.488536806</v>
+        <v>6292619</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,19 +751,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,19 +780,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103812230</v>
+        <v>103812208</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -843,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380924.1610734696</v>
+        <v>380952</v>
       </c>
       <c r="R3" t="n">
-        <v>6292555.740117267</v>
+        <v>6292599</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,19 +856,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,19 +885,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103812208</v>
+        <v>103812230</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380951.213766302</v>
+        <v>380924</v>
       </c>
       <c r="R4" t="n">
-        <v>6292598.842237333</v>
+        <v>6292556</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,19 +961,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,16 +993,11 @@
         <v>103812274</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380950.6335408181</v>
+        <v>380950</v>
       </c>
       <c r="R5" t="n">
-        <v>6292597.76195519</v>
+        <v>6292598</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,19 +1066,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22842-2022 artfynd.xlsx
+++ b/artfynd/A 22842-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103812205</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103812208</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103812230</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103812274</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>